--- a/01_Input/00_CO Validation/Cameroon, Republic of - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Cameroon, Republic of - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="178" documentId="11_654C6F3F109C81CED4A06B0578AE094E99EAC3E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{449806EA-3AE5-4983-88BA-2E27D6102BDA}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="11_654C6F3F109C81CED4A06B0578AE094E99EAC3E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{958B4CA8-B015-4849-BB1A-294043A09927}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,6 +15,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="117">
   <si>
     <t>Project ID</t>
   </si>
@@ -114,7 +117,7 @@
     <t>Energy (MW added)</t>
   </si>
   <si>
-    <t>KW</t>
+    <t>MW</t>
   </si>
   <si>
     <t>the health centers of Limani, Moskota, Kolofata and the district medical center of Amchide have benefited from the installation of solar kits to maintain the level of service and patient monitoring. These health center cover more than 10000 inhabitants. It was installed for the 5 health center, 10KW of solar energy</t>
@@ -152,9 +155,6 @@
   </si>
   <si>
     <t xml:space="preserve"> Allemagne  </t>
-  </si>
-  <si>
-    <t>MW</t>
   </si>
   <si>
     <t>Several administrations, security and justice services have been equipped with solar energy kits to power all their electrical circuits that were not supplied at the time. these are the sub-prefectures, police station, gendarmerie, customary courts, forestry posts, delegations of agriculture, livestock... this facilitates access to public services for more than 50,000 people in the different localities of Mozogo , Waza, Mora, Blangoua, Amchide, Kolofata. These installations have a total power of 63 KW</t>
@@ -196,7 +196,13 @@
     <t>UNDP CAMEROUN GOES GREEN: SUPPORT FOR THE ACHIEVEMENT OF SUSTAINABLE MOONSHOT OBJECTIVES</t>
   </si>
   <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
     <t>number of offices switching to led</t>
+  </si>
+  <si>
+    <t>1 building</t>
   </si>
   <si>
     <t>All (100%) the incandescents bulbs (offices, toilets, corridors, warehouse and building exteriors) of the main building of UNDP Cameroon.
@@ -219,6 +225,9 @@
 by the national company
 (ENEO) thanks to the
 installation of solar panels</t>
+  </si>
+  <si>
+    <t>2 building</t>
   </si>
   <si>
     <t>We had many zoom meetings with the OIMT Green
@@ -308,6 +317,9 @@
     <t>$40 000,00</t>
   </si>
   <si>
+    <t>KW</t>
+  </si>
+  <si>
     <t>$430 000,00</t>
   </si>
   <si>
@@ -517,7 +529,7 @@
       <name val="Helvetica Neue"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,8 +578,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -627,12 +645,122 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -671,6 +799,47 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -999,7 +1168,7 @@
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="17.7109375" customWidth="1"/>
-    <col min="9" max="9" width="46.5703125" customWidth="1"/>
+    <col min="9" max="9" width="62.28515625" customWidth="1"/>
     <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="13" max="13" width="47.5703125" customWidth="1"/>
     <col min="15" max="15" width="16.7109375" customWidth="1"/>
@@ -1066,16 +1235,16 @@
       </c>
     </row>
     <row r="2" spans="1:19" s="6" customFormat="1" ht="61.5">
-      <c r="A2" s="7">
+      <c r="A2" s="18">
         <v>118154</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="21">
         <v>1260000</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -1103,35 +1272,29 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="14" customFormat="1" ht="72.75">
-      <c r="A3" s="12">
-        <v>118154</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="12">
+    <row r="3" spans="1:19" s="6" customFormat="1" ht="51">
+      <c r="A3" s="19"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21">
         <v>40000</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="12">
-        <v>0</v>
-      </c>
-      <c r="H3" s="12">
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7">
         <v>0.05</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="7" t="s">
         <v>29</v>
       </c>
       <c r="O3" s="6" t="s">
@@ -1140,21 +1303,12 @@
       <c r="P3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-    </row>
-    <row r="4" spans="1:19" s="6" customFormat="1" ht="122.25">
-      <c r="A4" s="7">
-        <v>118154</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="7">
+    </row>
+    <row r="4" spans="1:19" s="6" customFormat="1" ht="102">
+      <c r="A4" s="24"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21">
         <v>430000</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -1176,17 +1330,11 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="6" customFormat="1" ht="61.5">
-      <c r="A5" s="7">
-        <v>118154</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="7">
+    <row r="5" spans="1:19" s="6" customFormat="1" ht="51">
+      <c r="A5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="21">
         <v>150000</v>
       </c>
       <c r="E5" s="6" t="s">
@@ -1208,35 +1356,29 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="14" customFormat="1" ht="110.25">
-      <c r="A6" s="12">
-        <v>118154</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="12">
+    <row r="6" spans="1:19" s="6" customFormat="1" ht="89.25">
+      <c r="A6" s="24"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="21">
         <v>200000</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>6.3E-2</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="12">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12">
-        <v>6.3E-2</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="7" t="s">
         <v>35</v>
       </c>
       <c r="O6" s="6" t="s">
@@ -1245,230 +1387,176 @@
       <c r="P6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-    </row>
-    <row r="7" spans="1:19" s="14" customFormat="1" ht="61.5">
-      <c r="A7" s="12">
-        <v>118154</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="13" t="s">
+    </row>
+    <row r="7" spans="1:19" s="6" customFormat="1" ht="51">
+      <c r="A7" s="24"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="21">
+        <v>7000</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="6" customFormat="1" ht="25.5">
+      <c r="A8" s="26"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="21">
+        <v>120000</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" s="6" customFormat="1" ht="208.5">
+      <c r="A9" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="12">
-        <v>7000</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="12">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-    </row>
-    <row r="8" spans="1:19" s="14" customFormat="1" ht="36.75">
-      <c r="A8" s="12">
-        <v>118154</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="D9" s="7">
+        <v>34255</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>70</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="6" customFormat="1" ht="216">
+      <c r="A10" s="18">
+        <v>130710</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="12">
-        <v>120000</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="12">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-    </row>
-    <row r="9" spans="1:19" s="14" customFormat="1" ht="208.5">
-      <c r="A9" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="12">
-        <v>34255</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="12">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12">
-        <v>70</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-    </row>
-    <row r="10" spans="1:19" s="14" customFormat="1" ht="256.5">
-      <c r="A10" s="12">
-        <v>130710</v>
-      </c>
-      <c r="B10" s="12" t="s">
+      <c r="D10" s="7">
+        <v>16839</v>
+      </c>
+      <c r="E10" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="12">
-        <v>16839</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="12">
-        <v>0</v>
-      </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12" t="s">
+      <c r="G10" s="7">
+        <v>0</v>
+      </c>
+      <c r="H10" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="I10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M10" s="15"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-    </row>
-    <row r="11" spans="1:19" s="14" customFormat="1" ht="409.6">
-      <c r="A11" s="12">
-        <v>130710</v>
-      </c>
-      <c r="B11" s="12" t="s">
+      <c r="J10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="31"/>
+    </row>
+    <row r="11" spans="1:19" s="6" customFormat="1" ht="409.6">
+      <c r="A11" s="19"/>
+      <c r="B11" s="22"/>
+      <c r="D11" s="21">
+        <v>57030</v>
+      </c>
+      <c r="E11" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="12">
-        <v>57030</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="12">
-        <v>0</v>
-      </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="M11" s="15"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-    </row>
-    <row r="12" spans="1:19" s="14" customFormat="1" ht="233.25">
-      <c r="A12" s="12">
-        <v>130710</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="17">
+      <c r="M11" s="31"/>
+    </row>
+    <row r="12" spans="1:19" s="6" customFormat="1" ht="203.25">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="33">
         <v>691</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="12">
+      <c r="F12" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="7">
         <v>124</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="7">
         <v>188</v>
       </c>
-      <c r="I12" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="M12" s="15"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
+      <c r="I12" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="31"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -1490,16 +1578,8 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{A547B403-9524-4A67-A0AB-97A27AA77374}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{FC7C051E-E24C-45D6-BE78-C89DF138FAEC}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{0A77659B-5F52-4810-AF65-9662545CB1D0}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{0AB08C00-DEB4-4DFC-882E-C5EA2473B1BF}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{862CFA62-C8BD-43D8-B974-D772B03B815D}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{8832BB69-3043-49C2-93BB-027DC99A7803}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{A86CD70F-BD68-4B24-9468-16E87E4C6BD0}"/>
-    <hyperlink ref="C9" r:id="rId8" xr:uid="{414ABE82-9F12-4F1F-8B95-426E879DE858}"/>
-    <hyperlink ref="C10" r:id="rId9" xr:uid="{D5D6AE8D-AF64-480C-AB65-C0BA1673BD19}"/>
-    <hyperlink ref="C11" r:id="rId10" xr:uid="{CB0A54C6-EF70-4B4D-81F4-A2254A81225F}"/>
-    <hyperlink ref="C12" r:id="rId11" xr:uid="{BD799CA2-FBDC-4CE9-A3B4-2E2C67C8CF2F}"/>
+    <hyperlink ref="C9" r:id="rId2" xr:uid="{414ABE82-9F12-4F1F-8B95-426E879DE858}"/>
+    <hyperlink ref="C10" r:id="rId3" xr:uid="{D5D6AE8D-AF64-480C-AB65-C0BA1673BD19}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1602,7 +1682,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>21</v>
@@ -1640,13 +1720,13 @@
         <v>20</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="G3" s="12">
         <v>0</v>
@@ -1681,7 +1761,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>32</v>
@@ -1713,7 +1793,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>36</v>
@@ -1745,13 +1825,13 @@
         <v>20</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G6" s="12">
         <v>0</v>
@@ -1760,7 +1840,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>35</v>
@@ -1786,13 +1866,13 @@
         <v>20</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G7" s="12">
         <v>0</v>
@@ -1801,10 +1881,10 @@
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="I7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>42</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>43</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1823,13 +1903,13 @@
         <v>20</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G8" s="12">
         <v>0</v>
@@ -1838,10 +1918,10 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="I8" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
@@ -1851,22 +1931,22 @@
     </row>
     <row r="9" spans="1:19" s="14" customFormat="1" ht="216">
       <c r="A9" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>47</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E9" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="12" t="s">
         <v>48</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>49</v>
       </c>
       <c r="G9" s="12">
         <v>0</v>
@@ -1875,10 +1955,10 @@
         <v>70</v>
       </c>
       <c r="I9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>51</v>
       </c>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
@@ -1891,13 +1971,13 @@
         <v>130710</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>26</v>
@@ -1910,10 +1990,10 @@
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M10" s="15"/>
       <c r="O10" s="6"/>
@@ -1927,29 +2007,29 @@
         <v>130710</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="12">
         <v>0</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M11" s="15"/>
       <c r="O11" s="6"/>
@@ -1963,7 +2043,7 @@
         <v>130710</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>20</v>
@@ -1975,19 +2055,19 @@
         <v>36</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H12" s="12">
         <v>188</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M12" s="15"/>
       <c r="O12" s="6"/>
@@ -2101,7 +2181,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>21</v>
@@ -2133,13 +2213,13 @@
         <v>20</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G3" s="7">
         <v>0</v>
@@ -2165,7 +2245,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>32</v>
@@ -2197,7 +2277,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>36</v>
@@ -2229,13 +2309,13 @@
         <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G6" s="7">
         <v>0</v>
@@ -2244,7 +2324,7 @@
         <v>31</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>35</v>
@@ -2261,13 +2341,13 @@
         <v>20</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G7" s="7">
         <v>0</v>
@@ -2276,10 +2356,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="6" customFormat="1" ht="38.25">
@@ -2293,13 +2373,13 @@
         <v>20</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G8" s="7">
         <v>0</v>
@@ -2308,56 +2388,56 @@
         <v>30</v>
       </c>
       <c r="I8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="6" customFormat="1" ht="216">
       <c r="A9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="I9" s="7" t="s">
+      <c r="J9" s="7" t="s">
         <v>50</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="6" customFormat="1" ht="228.75">
       <c r="A10" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>26</v>
@@ -2369,53 +2449,53 @@
         <v>0</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="6" customFormat="1" ht="409.6">
       <c r="A11" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="6" customFormat="1" ht="241.5">
       <c r="A12" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>20</v>
@@ -2427,19 +2507,19 @@
         <v>36</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2482,160 +2562,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="18" t="s">
-        <v>88</v>
+      <c r="A2" s="35" t="s">
+        <v>91</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="18"/>
+      <c r="A3" s="35"/>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="18"/>
+      <c r="A4" s="35"/>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="19" t="s">
-        <v>93</v>
+      <c r="A5" s="36" t="s">
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="19"/>
+      <c r="A6" s="36"/>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="19"/>
+      <c r="A7" s="36"/>
       <c r="B7" t="s">
         <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="19"/>
+      <c r="A8" s="36"/>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="19"/>
+      <c r="A9" s="36"/>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="20" t="s">
-        <v>100</v>
+      <c r="A10" s="37" t="s">
+        <v>103</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="20"/>
+      <c r="A11" s="37"/>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="21" t="s">
-        <v>104</v>
+      <c r="A12" s="38" t="s">
+        <v>107</v>
       </c>
       <c r="B12" t="s">
         <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="21"/>
+      <c r="A13" s="38"/>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="21"/>
+      <c r="A14" s="38"/>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/01_Input/00_CO Validation/Cameroon, Republic of - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Cameroon, Republic of - Energy Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27221"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28224"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="264" documentId="11_654C6F3F109C81CED4A06B0578AE094E99EAC3E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF0B265F-CAA2-44A9-9346-1633C4EA670B}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="11_654C6F3F109C81CED4A06B0578AE094E99EAC3E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03D05A16-9B50-4B13-9FA5-92771ADB2E6D}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="133">
   <si>
     <t>Project ID</t>
   </si>
@@ -99,6 +99,9 @@
     <t>Policy Population</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>Regional stabilization facility</t>
   </si>
   <si>
@@ -123,6 +126,15 @@
     <t>Accelerating just energy transition</t>
   </si>
   <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>National</t>
+  </si>
+  <si>
+    <t>Finalised</t>
+  </si>
+  <si>
     <t>Energy (MW added)</t>
   </si>
   <si>
@@ -133,9 +145,6 @@
   </si>
   <si>
     <t xml:space="preserve"> Japon </t>
-  </si>
-  <si>
-    <t>Solar</t>
   </si>
   <si>
     <t>Water Services</t>
@@ -149,6 +158,12 @@
   </si>
   <si>
     <t xml:space="preserve"> Japon, Allemagne  </t>
+  </si>
+  <si>
+    <t>Hydro</t>
+  </si>
+  <si>
+    <t>Community</t>
   </si>
   <si>
     <t>Capacity Building Training</t>
@@ -323,6 +338,9 @@
 So, at this step, we regularly observe more than more staff who turn off light when go out.</t>
   </si>
   <si>
+    <t>Other</t>
+  </si>
+  <si>
     <t>Category</t>
   </si>
   <si>
@@ -508,9 +526,6 @@
   </si>
   <si>
     <t xml:space="preserve">Number of people supported by policy and regulatory framework development on clean, affordable, and sustainable energy </t>
-  </si>
-  <si>
-    <t>Other</t>
   </si>
   <si>
     <t>Any other type of beneficiary (please specify justification in Notes)</t>
@@ -763,7 +778,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -865,6 +880,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1179,17 +1203,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8A16C56-5197-4C70-BCCF-E59A0D701BE3}">
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.85546875" customWidth="1"/>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="17.7109375" customWidth="1"/>
-    <col min="9" max="9" width="62.28515625" customWidth="1"/>
+    <col min="9" max="9" width="79.5703125" customWidth="1"/>
     <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -1201,9 +1225,10 @@
     <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1264,28 +1289,31 @@
       <c r="T1" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="34" t="s">
+      <c r="U1" s="44" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" s="40" customFormat="1" ht="49.5">
+      <c r="V1" s="34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" s="40" customFormat="1" ht="38.25">
       <c r="A2" s="15">
         <v>118154</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="18">
         <v>1260000</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="4">
         <v>0</v>
@@ -1294,28 +1322,35 @@
         <v>20000</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="42"/>
       <c r="L2" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="30"/>
       <c r="N2" s="36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O2" s="30"/>
       <c r="P2" s="30"/>
       <c r="Q2" s="30"/>
       <c r="R2" s="30"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="37"/>
-    </row>
-    <row r="3" spans="1:21" s="40" customFormat="1" ht="49.5">
+      <c r="S2" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="U2" s="45"/>
+      <c r="V2" s="47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" s="40" customFormat="1" ht="51">
       <c r="A3" s="16"/>
       <c r="B3" s="19"/>
       <c r="C3" s="20"/>
@@ -1323,10 +1358,10 @@
         <v>40000</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
@@ -1335,30 +1370,35 @@
         <v>0.05</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" s="30"/>
       <c r="N3" s="36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O3" s="30"/>
       <c r="P3" s="30"/>
       <c r="Q3" s="30"/>
       <c r="R3" s="30"/>
       <c r="S3" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="T3" s="35"/>
-      <c r="U3" s="3"/>
-    </row>
-    <row r="4" spans="1:21" s="40" customFormat="1" ht="97.5">
+        <v>30</v>
+      </c>
+      <c r="T3" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="U3" s="46"/>
+      <c r="V3" s="47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" s="40" customFormat="1" ht="76.5">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="20"/>
@@ -1366,10 +1406,10 @@
         <v>430000</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
@@ -1378,28 +1418,35 @@
         <v>5000</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M4" s="30"/>
       <c r="N4" s="36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O4" s="30"/>
       <c r="P4" s="30"/>
       <c r="Q4" s="30"/>
       <c r="R4" s="30"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="3"/>
-    </row>
-    <row r="5" spans="1:21" s="40" customFormat="1" ht="49.5">
+      <c r="S4" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="T4" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" s="46"/>
+      <c r="V4" s="47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" s="40" customFormat="1" ht="51">
       <c r="A5" s="21"/>
       <c r="B5" s="22"/>
       <c r="C5" s="20"/>
@@ -1407,10 +1454,10 @@
         <v>150000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G5" s="4">
         <v>0</v>
@@ -1419,28 +1466,35 @@
         <v>50</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M5" s="30"/>
       <c r="N5" s="36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O5" s="30"/>
       <c r="P5" s="30"/>
       <c r="Q5" s="30"/>
       <c r="R5" s="30"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="3"/>
-    </row>
-    <row r="6" spans="1:21" s="40" customFormat="1" ht="85.5">
+      <c r="S5" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="T5" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="U5" s="46"/>
+      <c r="V5" s="47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" s="40" customFormat="1" ht="63.75">
       <c r="A6" s="21"/>
       <c r="B6" s="22"/>
       <c r="C6" s="20"/>
@@ -1448,10 +1502,10 @@
         <v>200000</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
@@ -1460,30 +1514,35 @@
         <v>6.3E-2</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M6" s="30"/>
       <c r="N6" s="36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O6" s="30"/>
       <c r="P6" s="30"/>
       <c r="Q6" s="30"/>
       <c r="R6" s="30"/>
       <c r="S6" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="T6" s="35"/>
-      <c r="U6" s="3"/>
-    </row>
-    <row r="7" spans="1:21" s="40" customFormat="1" ht="49.5">
+        <v>30</v>
+      </c>
+      <c r="T6" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="U6" s="46"/>
+      <c r="V6" s="47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" s="40" customFormat="1" ht="38.25">
       <c r="A7" s="21"/>
       <c r="B7" s="22"/>
       <c r="C7" s="20"/>
@@ -1491,10 +1550,10 @@
         <v>7000</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G7" s="4">
         <v>0</v>
@@ -1503,30 +1562,35 @@
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M7" s="30"/>
       <c r="N7" s="36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O7" s="30"/>
       <c r="P7" s="30"/>
       <c r="Q7" s="30"/>
       <c r="R7" s="30"/>
       <c r="S7" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="T7" s="35"/>
-      <c r="U7" s="3"/>
-    </row>
-    <row r="8" spans="1:21" s="40" customFormat="1" ht="30.75">
+        <v>30</v>
+      </c>
+      <c r="T7" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="U7" s="46"/>
+      <c r="V7" s="47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" s="40" customFormat="1" ht="30.75">
       <c r="A8" s="23"/>
       <c r="B8" s="24"/>
       <c r="C8" s="25"/>
@@ -1534,10 +1598,10 @@
         <v>120000</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
@@ -1546,47 +1610,52 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M8" s="30"/>
       <c r="N8" s="36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O8" s="30"/>
       <c r="P8" s="30"/>
       <c r="Q8" s="30"/>
       <c r="R8" s="30"/>
       <c r="S8" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="T8" s="35"/>
-      <c r="U8" s="3"/>
-    </row>
-    <row r="9" spans="1:21" s="40" customFormat="1" ht="208.5">
+        <v>30</v>
+      </c>
+      <c r="T8" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="U8" s="46"/>
+      <c r="V8" s="47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" s="40" customFormat="1" ht="216">
       <c r="A9" s="26" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="4">
         <v>34255</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
@@ -1595,77 +1664,91 @@
         <v>70</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M9" s="30"/>
       <c r="N9" s="36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O9" s="30"/>
       <c r="P9" s="30"/>
       <c r="Q9" s="30"/>
       <c r="R9" s="30"/>
-      <c r="S9" s="37"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="3"/>
-    </row>
-    <row r="10" spans="1:21" s="40" customFormat="1" ht="208.5">
+      <c r="S9" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="T9" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="U9" s="46"/>
+      <c r="V9" s="47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" s="40" customFormat="1" ht="177.75">
       <c r="A10" s="15">
         <v>130710</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="4">
         <v>16839</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M10" s="30" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="N10" s="36" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="O10" s="30"/>
       <c r="P10" s="30"/>
       <c r="Q10" s="30"/>
       <c r="R10" s="30"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="3"/>
-    </row>
-    <row r="11" spans="1:21" s="40" customFormat="1" ht="409.6">
+      <c r="S10" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="T10" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="U10" s="46"/>
+      <c r="V10" s="47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" s="40" customFormat="1" ht="409.6">
       <c r="A11" s="16"/>
       <c r="B11" s="19"/>
       <c r="C11" s="3"/>
@@ -1673,42 +1756,49 @@
         <v>57030</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M11" s="30" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="N11" s="36" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="O11" s="30"/>
       <c r="P11" s="30"/>
       <c r="Q11" s="30"/>
       <c r="R11" s="30"/>
-      <c r="S11" s="37"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" s="40" customFormat="1" ht="195.75">
+      <c r="S11" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="T11" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="U11" s="46"/>
+      <c r="V11" s="47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" s="40" customFormat="1" ht="139.5">
       <c r="A12" s="23"/>
       <c r="B12" s="24"/>
       <c r="C12" s="25"/>
@@ -1716,10 +1806,10 @@
         <v>691</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G12" s="4">
         <v>124</v>
@@ -1728,26 +1818,33 @@
         <v>188</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M12" s="30"/>
       <c r="N12" s="36" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="O12" s="30"/>
       <c r="P12" s="30"/>
       <c r="Q12" s="30"/>
       <c r="R12" s="30"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="3"/>
+      <c r="S12" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="T12" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="U12" s="46"/>
+      <c r="V12" s="47" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="9">
@@ -1853,10 +1950,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>13</v>
@@ -1879,19 +1976,19 @@
         <v>118154</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="4">
         <v>0</v>
@@ -1900,16 +1997,16 @@
         <v>20000</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:19" s="11" customFormat="1" ht="76.5">
@@ -1917,19 +2014,19 @@
         <v>118154</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G3" s="9">
         <v>0</v>
@@ -1938,16 +2035,16 @@
         <v>0.05</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
@@ -1958,19 +2055,19 @@
         <v>118154</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
@@ -1979,10 +2076,10 @@
         <v>5000</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:19" s="3" customFormat="1" ht="63.75">
@@ -1990,19 +2087,19 @@
         <v>118154</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G5" s="4">
         <v>0</v>
@@ -2011,10 +2108,10 @@
         <v>50</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="11" customFormat="1" ht="114.75">
@@ -2022,19 +2119,19 @@
         <v>118154</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G6" s="9">
         <v>0</v>
@@ -2043,16 +2140,16 @@
         <v>6.3E-2</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -2063,19 +2160,19 @@
         <v>118154</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G7" s="9">
         <v>0</v>
@@ -2084,10 +2181,10 @@
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -2100,19 +2197,19 @@
         <v>118154</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G8" s="9">
         <v>0</v>
@@ -2121,10 +2218,10 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
@@ -2134,22 +2231,22 @@
     </row>
     <row r="9" spans="1:19" s="11" customFormat="1" ht="216">
       <c r="A9" s="9" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G9" s="9">
         <v>0</v>
@@ -2158,10 +2255,10 @@
         <v>70</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -2174,29 +2271,29 @@
         <v>130710</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G10" s="9">
         <v>0</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M10" s="12"/>
       <c r="O10" s="3"/>
@@ -2210,29 +2307,29 @@
         <v>130710</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G11" s="9">
         <v>0</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="M11" s="12"/>
       <c r="O11" s="3"/>
@@ -2246,31 +2343,31 @@
         <v>130710</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="14">
         <v>691</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H12" s="9">
         <v>188</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M12" s="12"/>
       <c r="O12" s="3"/>
@@ -2378,19 +2475,19 @@
         <v>118154</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="4">
         <v>0</v>
@@ -2399,10 +2496,10 @@
         <v>20000</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" ht="76.5">
@@ -2410,19 +2507,19 @@
         <v>118154</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
@@ -2431,10 +2528,10 @@
         <v>4</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" ht="126.75">
@@ -2442,19 +2539,19 @@
         <v>118154</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
@@ -2463,10 +2560,10 @@
         <v>5000</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" ht="63.75">
@@ -2474,19 +2571,19 @@
         <v>118154</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G5" s="4">
         <v>0</v>
@@ -2495,10 +2592,10 @@
         <v>50</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" ht="114.75">
@@ -2506,19 +2603,19 @@
         <v>118154</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
@@ -2527,10 +2624,10 @@
         <v>31</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" ht="63.75">
@@ -2538,19 +2635,19 @@
         <v>118154</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G7" s="4">
         <v>0</v>
@@ -2559,10 +2656,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" ht="38.25">
@@ -2570,19 +2667,19 @@
         <v>118154</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
@@ -2591,138 +2688,138 @@
         <v>30</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" ht="216">
       <c r="A9" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" ht="228.75">
       <c r="A10" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" ht="409.6">
       <c r="A11" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" ht="241.5">
       <c r="A12" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="5">
         <v>691</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2772,171 +2869,171 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="43" t="s">
-        <v>69</v>
+      <c r="A2" s="48" t="s">
+        <v>75</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="43" t="s">
-        <v>29</v>
+      <c r="A3" s="48" t="s">
+        <v>33</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="43" t="s">
-        <v>100</v>
+      <c r="A4" s="48" t="s">
+        <v>106</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="43" t="s">
-        <v>102</v>
+      <c r="A5" s="48" t="s">
+        <v>108</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="43" t="s">
-        <v>104</v>
+      <c r="A6" s="48" t="s">
+        <v>110</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="43" t="s">
-        <v>84</v>
+      <c r="A7" s="48" t="s">
+        <v>90</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="43" t="s">
-        <v>34</v>
+      <c r="A8" s="48" t="s">
+        <v>37</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="43" t="s">
-        <v>88</v>
+      <c r="A9" s="48" t="s">
+        <v>94</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>110</v>
+      <c r="A10" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="49" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45.75">
+      <c r="A12" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30.75">
+      <c r="A13" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30.75">
+      <c r="A15" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30.75">
+      <c r="A16" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30.75">
+      <c r="A17" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30.75">
+      <c r="A18" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="44" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="44" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="44" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" s="44" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="44" t="s">
-        <v>120</v>
+      <c r="B18" s="49" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="44" t="s">
-        <v>122</v>
+      <c r="A19" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="B20" s="44" t="s">
-        <v>124</v>
+      <c r="A20" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="45" t="s">
-        <v>125</v>
+      <c r="B21" s="50" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" s="44" t="s">
-        <v>127</v>
+      <c r="A22" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2945,8 +3042,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2971,6 +3077,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3050,6 +3157,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3193,15 +3305,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3209,16 +3312,53 @@
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
     <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Larissa Tuayo</DisplayName>
+        <AccountId>1385</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jose LEVY</DisplayName>
+        <AccountId>175</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Martin Hart-Hansen</DisplayName>
+        <AccountId>2563</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fungai Matura</DisplayName>
+        <AccountId>1028</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Benjamin Keller</DisplayName>
+        <AccountId>1227</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Tannya Quinza-armenta</DisplayName>
+        <AccountId>2508</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D569386E-0380-42F0-931E-E1D122B6EE01}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C856DEAA-7A2A-4316-A2A6-117294EDA77C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C856DEAA-7A2A-4316-A2A6-117294EDA77C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21B6F43A-8EEB-4070-9CAD-73A8729CAC45}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Cameroon, Republic of - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Cameroon, Republic of - Energy Projects.xlsx
@@ -1727,7 +1727,7 @@
       <c r="X12" s="46" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -1754,12 +1754,6 @@
     </dataValidation>
     <dataValidation sqref="R2:R12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
